--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-lagos.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M389"/>
+  <dimension ref="A1:M394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28260.91</v>
+        <v>28021.55</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7834.16</v>
+        <v>7755.97</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3028.27</v>
+        <v>2996.55</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1925.19</v>
+        <v>1914.67</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4638.18</v>
+        <v>4612.82</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1718.58</v>
+        <v>1709.18</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1246.09</v>
+        <v>1239.26</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1691.47</v>
+        <v>1682.2</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8088.51</v>
+        <v>8044.22</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>21009.1</v>
+        <v>20894.04</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1616.99</v>
+        <v>1614.93</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1676.14</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1296.45</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2151.91</v>
+        <v>2149.17</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4781.63</v>
+        <v>4798.7</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1432.71</v>
+        <v>1448.3</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2027.08</v>
+        <v>2049.12</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1082.07</v>
+        <v>1093.84</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>850.61</v>
+        <v>859.87</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3229.73</v>
+        <v>3240.35</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>998.8099999999999</v>
+        <v>1002.1</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>921.72</v>
+        <v>937.63</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>956.01</v>
+        <v>972.51</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2671.78</v>
+        <v>2717.9</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1167.11</v>
+        <v>1175.2</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5557.36</v>
+        <v>5583.24</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2149.94</v>
+        <v>2159.95</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1663.65</v>
+        <v>1675.64</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>776.7</v>
+        <v>782.3</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1225.46</v>
+        <v>1234.29</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9535.969999999999</v>
+        <v>9604.719999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1228.44</v>
+        <v>1226.26</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3517.01</v>
+        <v>3510.77</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>834.26</v>
+        <v>838.5700000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>834.03</v>
+        <v>838.34</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3812.95</v>
+        <v>3839.86</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4756.85</v>
+        <v>4790.42</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>759.15</v>
+        <v>749.34</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>785.1799999999999</v>
+        <v>775.03</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>925.59</v>
+        <v>913.63</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2732.2</v>
+        <v>2697.49</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>869.35</v>
+        <v>858.3099999999999</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1166.08</v>
+        <v>1151.27</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1746.7</v>
+        <v>1729.32</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2184.58</v>
+        <v>2176.75</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>43697.42</v>
+        <v>43540.73</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5366.4</v>
+        <v>5347.16</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>15241.67</v>
+        <v>15208.68</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>9813.93</v>
+        <v>9792.700000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2663.42</v>
+        <v>2652.26</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1983.11</v>
+        <v>1966.31</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>789.66</v>
+        <v>782.97</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2561.23</v>
+        <v>2539.53</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3469.23</v>
+        <v>3466.44</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4302.44</v>
+        <v>4298.98</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>881.95</v>
+        <v>885.34</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1262.59</v>
+        <v>1267.43</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>815.97</v>
+        <v>819.66</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>833.42</v>
+        <v>835.63</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11175.96</v>
+        <v>11205.59</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1336.71</v>
+        <v>1334.83</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2663.77</v>
+        <v>2660.04</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3194.26</v>
+        <v>3189.78</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>75640.87</v>
+        <v>75534.75999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1653.33</v>
+        <v>1655.44</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>781.77</v>
+        <v>782.77</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>785.65</v>
+        <v>786.66</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2771.11</v>
+        <v>2790.18</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1038.43</v>
+        <v>1045.58</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8151.87</v>
+        <v>8239.309999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1082.92</v>
+        <v>1096.23</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4651.05</v>
+        <v>4708.21</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>25061.64</v>
+        <v>25369.65</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>27243.76</v>
+        <v>27578.59</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>13097.8</v>
+        <v>13258.78</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>12736.74</v>
+        <v>12893.28</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>36285.3</v>
+        <v>36751.55</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>41696.81</v>
+        <v>42232.6</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>785.1799999999999</v>
+        <v>795.27</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3475.4</v>
+        <v>3386.65</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3618.6</v>
+        <v>3533.95</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5521.6</v>
+        <v>5442.03</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2698.34</v>
+        <v>2659.45</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1263.68</v>
+        <v>1245.47</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>912.8</v>
+        <v>901</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1467.12</v>
+        <v>1464.23</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>968.91</v>
+        <v>967</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>917.5700000000001</v>
+        <v>915.77</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>891.73</v>
+        <v>889.97</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3774.98</v>
+        <v>3767.54</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1165.36</v>
+        <v>1165.37</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3134.85</v>
+        <v>3139.21</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2118.74</v>
+        <v>2121.68</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>7236.53</v>
+        <v>7246.58</v>
       </c>
     </row>
     <row r="96">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1030.15</v>
+        <v>1031.58</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3289-2-CM26</t>
+          <t>3888-28-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6329,17 +6329,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3839.49</v>
+        <v>3975.29</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3888-28-CM26</t>
+          <t>3289-2-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3978</v>
+        <v>3836.86</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>13390.04</v>
+        <v>13380.89</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1556.34</v>
+        <v>1548.11</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1133.03</v>
+        <v>1127.05</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1641.63</v>
+        <v>1632.96</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2749.81</v>
+        <v>2732.58</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3541.6</v>
+        <v>3519.41</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3732.98</v>
+        <v>3709.59</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4491.86</v>
+        <v>4463.71</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1764.01</v>
+        <v>1752.96</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>8929.940000000001</v>
+        <v>8873.98</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1600.64</v>
+        <v>1611.13</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>27324.13</v>
+        <v>27503.21</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1367.75</v>
+        <v>1386.16</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1466.76</v>
+        <v>1486.51</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2591.49</v>
+        <v>2630.94</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5521.6</v>
+        <v>5605.66</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1196.35</v>
+        <v>1214.56</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3168.77</v>
+        <v>3217.01</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4958.08</v>
+        <v>5078.65</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7928.17</v>
+        <v>8128.6</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4617.92</v>
+        <v>4734.66</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2275.09</v>
+        <v>2332.6</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>5129.05</v>
+        <v>5258.71</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6529.1</v>
+        <v>6694.16</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2755.33</v>
+        <v>2824.99</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>13857.99</v>
+        <v>14278.21</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>73352.41</v>
+        <v>75576.67999999999</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3880.44</v>
+        <v>3995.78</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2327.59</v>
+        <v>2396.77</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5896.23</v>
+        <v>5852.1</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>822.5599999999999</v>
+        <v>816.4</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>817.8</v>
+        <v>820.16</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4214.07</v>
+        <v>4226.28</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1494.97</v>
+        <v>1499.3</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7016.14</v>
+        <v>7052.38</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>12184.66</v>
+        <v>12247.6</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>29168.32</v>
+        <v>29318.99</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2842.44</v>
+        <v>2857.12</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6056.87</v>
+        <v>6088.16</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1019.83</v>
+        <v>1025.1</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1627.53</v>
+        <v>1620.67</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>10328.74</v>
+        <v>10285.19</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2988.26</v>
+        <v>2975.66</v>
       </c>
     </row>
     <row r="142">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2128.49</v>
+        <v>2134.33</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3479-213-CM26</t>
+          <t>3510-83-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>Departamento de Educación</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4764.4</v>
+        <v>2341.73</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2912-62-CM26</t>
+          <t>3479-213-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,17 +9196,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>8433.85</v>
+        <v>4807.74</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1161-49-CM26</t>
+          <t>2912-62-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9257,17 +9257,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Departamento Administrativo de Salud Municipal.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1613.01</v>
+        <v>8510.57</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3510-83-CM26</t>
+          <t>1161-49-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2320.63</v>
+        <v>1627.69</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>6799.62</v>
+        <v>6846.96</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>24765.78</v>
+        <v>24938.21</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3610.43</v>
+        <v>3642.59</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>6178.55</v>
+        <v>6233.58</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>944.65</v>
+        <v>953.0599999999999</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2417.38</v>
+        <v>2414.89</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>815.51</v>
+        <v>814.67</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>955.03</v>
+        <v>954.04</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1280.7</v>
+        <v>1271.52</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>9547.209999999999</v>
+        <v>9533.16</v>
       </c>
     </row>
     <row r="157">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>815.13</v>
+        <v>813.9299999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4906-42-CM26</t>
+          <t>387-121-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.980.740-5</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1771.93</v>
+        <v>3498.85</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>387-121-CM26</t>
+          <t>4906-42-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.980.740-5</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3518.01</v>
+        <v>1762.28</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1057536-499-CM26</t>
+          <t>1063538-1681-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4432.54</v>
+        <v>5628.8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1063538-1681-CM26</t>
+          <t>1057536-499-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5662.17</v>
+        <v>4406.42</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>868.24</v>
+        <v>872.74</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1471.41</v>
+        <v>1479.03</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2415.8</v>
+        <v>2418.13</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1790.48</v>
+        <v>1792.21</v>
       </c>
     </row>
     <row r="166">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>821.65</v>
+        <v>822.4400000000001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2137-161-CM26</t>
+          <t>2328-149-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1185.28</v>
+        <v>3085.43</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2328-151-CM26</t>
+          <t>2328-150-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>OPEN SANTIAGO SPA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>78.069.505-6</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1189.4</v>
+        <v>3038.37</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1224974-32-CM26</t>
+          <t>2328-151-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10721,17 +10721,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>65.137.070-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>OPEN SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.069.505-6</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>779.9400000000001</v>
+        <v>1241.93</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2328-149-CM26</t>
+          <t>2137-161-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2954.93</v>
+        <v>1237.62</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2328-150-CM26</t>
+          <t>1224974-32-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10843,17 +10843,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>65.137.070-1</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>CORP CULTURAL DE OSORNO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2909.87</v>
+        <v>814.38</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2165.01</v>
+        <v>2227.89</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1193.38</v>
+        <v>1198.09</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1113.69</v>
+        <v>1118.08</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>5293.38</v>
+        <v>5314.24</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1054.62</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>776.6</v>
+        <v>778.51</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1365.35</v>
+        <v>1368.71</v>
       </c>
     </row>
     <row r="179">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>6116.16</v>
+        <v>6131.21</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1079639-122-CM26</t>
+          <t>1057539-1299-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>54694.11</v>
+        <v>1291.02</v>
       </c>
     </row>
     <row r="181">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1885.39</v>
+        <v>1861.12</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1057539-1299-CM26</t>
+          <t>1079639-122-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1307.86</v>
+        <v>53989.98</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2306-69-CM26</t>
+          <t>3510-204-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11575,17 +11575,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>Departamento de Educación</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1602.86</v>
+        <v>1561.93</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2306-71-CM26</t>
+          <t>2887-46-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2982.9</v>
+        <v>768.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1663-193-CM26</t>
+          <t>1071775-17-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11697,17 +11697,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3064.28</v>
+        <v>1606.97</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2306-76-CM26</t>
+          <t>2887-44-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>79.668.170-5</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>5157.12</v>
+        <v>918.21</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2887-44-CM26</t>
+          <t>2306-71-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>924.74</v>
+        <v>2961.85</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1071775-17-CM26</t>
+          <t>1663-193-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>Hospital de Quellón</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1618.39</v>
+        <v>3042.66</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2887-46-CM26</t>
+          <t>2306-69-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>773.67</v>
+        <v>1591.54</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3510-204-CM26</t>
+          <t>2306-76-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12002,17 +12002,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1573.03</v>
+        <v>5120.73</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>545598-141-CM26</t>
+          <t>4195-284-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>69.230.200-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>I MUNICIPALIDAD DE QUEMCHI</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4953.15</v>
+        <v>1211.25</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4195-284-CM26</t>
+          <t>545598-141-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.230.200-1</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1189.68</v>
+        <v>5042.96</v>
       </c>
     </row>
     <row r="193">
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1900.42</v>
+        <v>1930.19</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2306-84-CM26</t>
+          <t>2306-86-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>13410.25</v>
+        <v>19368.03</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2306-86-CM26</t>
+          <t>2095-10-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12307,17 +12307,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>19369.03</v>
+        <v>1757.55</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2095-10-CM26</t>
+          <t>2306-84-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12368,17 +12368,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1757.65</v>
+        <v>13409.56</v>
       </c>
     </row>
     <row r="197">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1002.69</v>
+        <v>1002.64</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1663-218-CM26</t>
+          <t>1663-208-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>79.668.170-5</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>4701.37</v>
+        <v>6879.74</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1663-208-CM26</t>
+          <t>1663-218-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>6880.1</v>
+        <v>4701.13</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1715.93</v>
+        <v>1717.41</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3999.05</v>
+        <v>4002.5</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1188.26</v>
+        <v>1193.16</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>776.78</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4584.52</v>
+        <v>4603.45</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1277.53</v>
+        <v>1262.78</v>
       </c>
     </row>
     <row r="206">
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2220.58</v>
+        <v>2194.94</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3289-24-CM26</t>
+          <t>1224953-185-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13039,17 +13039,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>71.420.700-8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>964.95</v>
+        <v>3162.44</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5110-87-CM26</t>
+          <t>4180-48-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13100,17 +13100,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Carabineros de Chile - X Zona Los Lagos</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2659.5</v>
+        <v>3177.88</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1224953-185-CM26</t>
+          <t>5110-87-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>71.420.700-8</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3210.33</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4180-48-CM26</t>
+          <t>3289-24-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3226</v>
+        <v>950.5599999999999</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3507-203-CM26</t>
+          <t>2324-382-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13283,17 +13283,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>79.668.170-5</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1259</v>
+        <v>868.75</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2324-382-CM26</t>
+          <t>3507-203-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13344,17 +13344,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>Departamento de Salud</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>873.77</v>
+        <v>1251.76</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1236.96</v>
+        <v>1229.04</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5364.26</v>
+        <v>5329.89</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1227.81</v>
+        <v>1222.52</v>
       </c>
     </row>
     <row r="216">
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1787.56</v>
+        <v>1761.7</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1079639-202-CM26</t>
+          <t>2306-121-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13649,17 +13649,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3352.04</v>
+        <v>12563.57</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2324-411-CM26</t>
+          <t>2658-430-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13710,17 +13710,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1385.6</v>
+        <v>2068.01</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2306-121-CM26</t>
+          <t>1079639-202-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13771,17 +13771,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>12839.82</v>
+        <v>3279.92</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2658-430-CM26</t>
+          <t>2324-411-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13832,17 +13832,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2113.48</v>
+        <v>1355.79</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>873.9</v>
+        <v>853.5700000000001</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1765.72</v>
+        <v>1724.64</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2445.11</v>
+        <v>2367.14</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>6010.92</v>
+        <v>5892.38</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1495.57</v>
+        <v>1466.08</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1273.32</v>
+        <v>1248.21</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2979.5</v>
+        <v>2901.04</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>796.13</v>
+        <v>775.16</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>894.6</v>
+        <v>871.04</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1888.71</v>
+        <v>1854.46</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1777.78</v>
+        <v>1730.18</v>
       </c>
     </row>
     <row r="232">
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>9942.129999999999</v>
+        <v>9971.07</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>696954-13-CM26</t>
+          <t>3510-320-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14625,17 +14625,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Departamento de Educación</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>4966.03</v>
+        <v>782.4</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3510-320-CM26</t>
+          <t>2852-255-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>779.16</v>
+        <v>3544.69</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2852-255-CM26</t>
+          <t>696954-13-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14747,17 +14747,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3530.02</v>
+        <v>4986.67</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>809.35</v>
+        <v>816.22</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>945.73</v>
+        <v>953.75</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>4961.39</v>
+        <v>4953.1</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>923.28</v>
+        <v>934.64</v>
       </c>
     </row>
     <row r="240">
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>12575.97</v>
+        <v>12743.39</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2940-41-CM26</t>
+          <t>2297-474-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.210.201-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3498.41</v>
+        <v>4775.74</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2306-209-CM26</t>
+          <t>2306-208-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>79.668.170-5</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>12608</v>
+        <v>10052.27</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2989-215-CM26</t>
+          <t>2306-209-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1604.19</v>
+        <v>12772.53</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2297-474-CM26</t>
+          <t>2940-41-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.210.201-0</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>IMunicipalidad de San Pablo - Educación</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4714.22</v>
+        <v>3544.06</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2306-208-CM26</t>
+          <t>2989-215-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>9922.780000000001</v>
+        <v>1625.12</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1057539-2635-CM26</t>
+          <t>707425-74-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15418,17 +15418,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>838.6799999999999</v>
+        <v>1208.98</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2730-176-CM26</t>
+          <t>2306-196-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15479,17 +15479,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>925.54</v>
+        <v>1209.06</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2306-196-CM26</t>
+          <t>2730-176-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15540,17 +15540,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1180.02</v>
+        <v>948.3200000000001</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>707425-74-CM26</t>
+          <t>1057539-2635-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15601,17 +15601,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1179.95</v>
+        <v>859.3200000000001</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1428.88</v>
+        <v>1455.9</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1039.99</v>
+        <v>1049.36</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>4671.28</v>
+        <v>4701.15</v>
       </c>
     </row>
     <row r="253">
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2322.86</v>
+        <v>2337.71</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1063538-3318-CM26</t>
+          <t>4042-88-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15906,17 +15906,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>69.220.402-6</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>Ilustre Municipalidad de Fresia - Salud</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15926,12 +15926,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>6157.29</v>
+        <v>3870.72</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>752-102-CM26</t>
+          <t>162-128-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15972,12 +15972,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>781.95</v>
+        <v>794.09</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>853-84-CM26</t>
+          <t>162-131-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>9341.870000000001</v>
+        <v>784.7</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4042-88-CM26</t>
+          <t>853-84-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16089,17 +16089,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.220.402-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16109,12 +16109,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3858.58</v>
+        <v>9371.26</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>162-128-CM26</t>
+          <t>752-102-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16155,12 +16155,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>791.6</v>
+        <v>784.41</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>162-131-CM26</t>
+          <t>1063538-3318-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>782.23</v>
+        <v>6176.66</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2048-1200-CM26</t>
+          <t>1970-23-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16277,12 +16277,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16292,12 +16292,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>3005.86</v>
+        <v>795.41</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1518-7-CM26</t>
+          <t>1518-8-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>982.01</v>
+        <v>876.8</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1518-8-CM26</t>
+          <t>2048-1200-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.818.004-2</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Delegación Provincial Osorno</t>
+          <t>Hospital de Ancud</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16429,13 +16429,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>873.1799999999999</v>
+        <v>3018.32</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1970-23-CM26</t>
+          <t>1518-7-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.818.004-2</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Delegación Provincial Osorno</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>792.13</v>
+        <v>986.09</v>
       </c>
     </row>
     <row r="264">
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>15531.47</v>
+        <v>15563.64</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1057534-531-CM26</t>
+          <t>162-165-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16582,12 +16582,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1305.29</v>
+        <v>1145.09</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2940-56-CM26</t>
+          <t>1740-16-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16638,17 +16638,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.210.201-0</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16673,13 +16673,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1195.98</v>
+        <v>783.34</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>162-165-CM26</t>
+          <t>1057534-531-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16704,12 +16704,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16734,13 +16734,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1160.88</v>
+        <v>1287.54</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1740-16-CM26</t>
+          <t>2940-56-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16760,17 +16760,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>69.210.201-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>IMunicipalidad de San Pablo - Educación</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16780,12 +16780,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>794.14</v>
+        <v>1179.72</v>
       </c>
     </row>
     <row r="269">
@@ -16856,13 +16856,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>874.83</v>
+        <v>867.37</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2306-273-CM26</t>
+          <t>3508-414-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16887,12 +16887,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.230.500-0</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CHONCHI</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -16917,13 +16917,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2505.48</v>
+        <v>2755.31</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1126922-510-CM26</t>
+          <t>1057534-555-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16948,12 +16948,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16963,12 +16963,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1030.27</v>
+        <v>810.5599999999999</v>
       </c>
     </row>
     <row r="272">
@@ -17039,13 +17039,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>865.76</v>
+        <v>870.42</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1057534-555-CM26</t>
+          <t>1126922-510-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17085,12 +17085,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17100,13 +17100,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>806.22</v>
+        <v>1035.82</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3508-414-CM26</t>
+          <t>2306-273-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.230.500-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHONCHI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17146,12 +17146,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2740.56</v>
+        <v>2518.98</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3150.45</v>
+        <v>3185.69</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5838.39</v>
+        <v>5903.68</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>3271.96</v>
+        <v>3308.56</v>
       </c>
     </row>
     <row r="278">
@@ -17405,13 +17405,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>812.0700000000001</v>
+        <v>818.22</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1126922-554-CM26</t>
+          <t>2136-310-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.602.270-9</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17466,13 +17466,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>951.1900000000001</v>
+        <v>782.76</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2136-310-CM26</t>
+          <t>2306-302-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17492,17 +17492,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.602.270-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17527,13 +17527,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>779.8099999999999</v>
+        <v>4831.3</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2306-302-CM26</t>
+          <t>1126922-554-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17553,17 +17553,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4813.07</v>
+        <v>954.79</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1224953-310-CM26</t>
+          <t>2306-301-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17619,12 +17619,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>71.420.700-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>3725.61</v>
+        <v>4040.62</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2306-301-CM26</t>
+          <t>2306-308-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4050.85</v>
+        <v>2700.97</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2306-308-CM26</t>
+          <t>1224953-310-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17741,12 +17741,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>71.420.700-8</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17756,12 +17756,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2707.81</v>
+        <v>3716.21</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4404.64</v>
+        <v>4446.49</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1521.24</v>
+        <v>1535.7</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2573.12</v>
+        <v>2597.56</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>809.42</v>
+        <v>817.11</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>6969.08</v>
+        <v>7021</v>
       </c>
     </row>
     <row r="290">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>878.3</v>
+        <v>884.85</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2306-341-CM26</t>
+          <t>1057539-3519-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18168,12 +18168,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>8803.959999999999</v>
+        <v>17167.25</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2306-337-CM26</t>
+          <t>2852-415-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18229,12 +18229,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18244,12 +18244,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18259,13 +18259,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>13078.18</v>
+        <v>2524.18</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2852-415-CM26</t>
+          <t>2306-337-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18305,12 +18305,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18320,13 +18320,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2549.6</v>
+        <v>12947.75</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1057539-3519-CM26</t>
+          <t>2306-341-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>9.681.827-0</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>17340.18</v>
+        <v>8716.16</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2332-506-CM26</t>
+          <t>2332-529-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18427,12 +18427,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18442,13 +18442,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>15407.3</v>
+        <v>3508.66</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2332-529-CM26</t>
+          <t>2332-506-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18488,12 +18488,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3524.11</v>
+        <v>15339.77</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>7321.11</v>
+        <v>7357.07</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1331.04</v>
+        <v>1337.58</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1996.77</v>
+        <v>2006.57</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>813.3200000000001</v>
+        <v>816.02</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3412.3</v>
+        <v>3423.16</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2081.27</v>
+        <v>2087.89</v>
       </c>
     </row>
     <row r="303">
@@ -18930,13 +18930,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>840.1</v>
+        <v>842.77</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2028-37-CM26</t>
+          <t>584146-222-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18956,17 +18956,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>60.902.039-3</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Llanquihue</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18976,12 +18976,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -18991,13 +18991,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>3830.19</v>
+        <v>808.77</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>584146-222-CM26</t>
+          <t>2028-37-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19017,17 +19017,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>60.902.039-3</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Depto. Provincial Educación Llanquihue</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19037,12 +19037,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>804.49</v>
+        <v>3850.55</v>
       </c>
     </row>
     <row r="306">
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1021.46</v>
+        <v>1033.44</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1057539-4101-CM26</t>
+          <t>2306-431-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19144,12 +19144,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19159,12 +19159,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>9.681.827-0</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19174,13 +19174,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>3712.42</v>
+        <v>5409.88</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1057539-4102-CM26</t>
+          <t>4906-134-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19205,12 +19205,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.980.740-5</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19220,12 +19220,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19235,13 +19235,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1191.74</v>
+        <v>961.34</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1057536-1565-CM26</t>
+          <t>2730-279-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19266,12 +19266,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -19296,13 +19296,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1685.19</v>
+        <v>3050.92</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2730-279-CM26</t>
+          <t>1057539-4102-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19327,12 +19327,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19357,13 +19357,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3000.18</v>
+        <v>1211.89</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>4906-134-CM26</t>
+          <t>1057539-4101-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19388,12 +19388,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.980.740-5</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>945.35</v>
+        <v>3775.2</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2306-431-CM26</t>
+          <t>1057536-1565-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19449,12 +19449,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19464,12 +19464,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -19479,13 +19479,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>5319.91</v>
+        <v>1713.69</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1126922-711-CM26</t>
+          <t>1057539-4149-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19505,17 +19505,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19525,12 +19525,12 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -19540,13 +19540,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1131.28</v>
+        <v>1483.66</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1126922-709-CM26</t>
+          <t>1057539-4150-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19571,12 +19571,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19586,12 +19586,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1132.85</v>
+        <v>1320.95</v>
       </c>
     </row>
     <row r="315">
@@ -19662,13 +19662,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2834.24</v>
+        <v>2863.06</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1057539-4150-CM26</t>
+          <t>1126922-709-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19693,12 +19693,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19708,12 +19708,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>9.681.827-0</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19723,13 +19723,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1307.65</v>
+        <v>1144.37</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1057539-4149-CM26</t>
+          <t>1126922-711-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19749,17 +19749,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>9.681.827-0</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1468.73</v>
+        <v>1142.79</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1565.9</v>
+        <v>1580.59</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>3479.01</v>
+        <v>3511.64</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2611.77</v>
+        <v>2591.96</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1032.86</v>
+        <v>1015.41</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2396.51</v>
+        <v>2362.5</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>926.9</v>
+        <v>914.16</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1930.95</v>
+        <v>1918.98</v>
       </c>
     </row>
     <row r="325">
@@ -20272,13 +20272,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>977.4400000000001</v>
+        <v>971.38</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2297-777-CM26</t>
+          <t>2306-349-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20318,12 +20318,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>953.83</v>
+        <v>4464.32</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2306-349-CM26</t>
+          <t>2306-420-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20394,13 +20394,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4381.03</v>
+        <v>5805.07</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2306-420-CM26</t>
+          <t>2297-777-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20440,12 +20440,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>5696.76</v>
+        <v>971.97</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1078.21</v>
+        <v>1102.53</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1581.9</v>
+        <v>1617.58</v>
       </c>
     </row>
     <row r="331">
@@ -20638,13 +20638,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2392.13</v>
+        <v>2446.08</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>387-369-CM26</t>
+          <t>707425-113-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20669,12 +20669,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20684,12 +20684,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -20699,13 +20699,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2511.06</v>
+        <v>2619.86</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2137-504-CM26</t>
+          <t>387-369-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20730,12 +20730,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20745,12 +20745,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K333" t="inlineStr"/>
@@ -20760,13 +20760,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>844.9400000000001</v>
+        <v>2528.4</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>707425-113-CM26</t>
+          <t>2137-504-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20791,12 +20791,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20821,13 +20821,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2601.89</v>
+        <v>850.77</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1126922-820-CM26</t>
+          <t>1057532-962-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20847,17 +20847,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20867,12 +20867,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -20882,13 +20882,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1263.89</v>
+        <v>811.3</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1057532-962-CM26</t>
+          <t>1126922-820-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20908,17 +20908,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20928,12 +20928,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>79.668.170-5</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -20943,13 +20943,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>808.8</v>
+        <v>1267.8</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>853-121-CM26</t>
+          <t>853-119-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21004,13 +21004,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>13232.83</v>
+        <v>22296.4</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>3888-455-CM26</t>
+          <t>853-120-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21030,17 +21030,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21050,12 +21050,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -21065,13 +21065,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1471.73</v>
+        <v>10931.62</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>853-119-CM26</t>
+          <t>853-121-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21126,13 +21126,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>22355.53</v>
+        <v>13197.83</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>853-120-CM26</t>
+          <t>3888-455-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21152,17 +21152,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21172,12 +21172,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K340" t="inlineStr"/>
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>10960.61</v>
+        <v>1467.84</v>
       </c>
     </row>
     <row r="341">
@@ -21248,13 +21248,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>10954.41</v>
+        <v>10808.49</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5110-232-CM26</t>
+          <t>3507-440-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21279,12 +21279,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Departamento de Salud</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2105</v>
+        <v>825.38</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>3507-440-CM26</t>
+          <t>5110-232-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21340,12 +21340,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>841.85</v>
+        <v>2063.79</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2058.33</v>
+        <v>2018.04</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1374.32</v>
+        <v>1353.96</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1335.92</v>
+        <v>1308.47</v>
       </c>
     </row>
     <row r="347">
@@ -21614,13 +21614,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>956.36</v>
+        <v>960.1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1173430-105-CM26</t>
+          <t>1662-1334-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.950.500-K</t>
+          <t>61.602.273-3</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21675,13 +21675,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1488.3</v>
+        <v>855.1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1057534-867-CM26</t>
+          <t>1057534-866-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -21721,12 +21721,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -21736,13 +21736,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1177.31</v>
+        <v>793.63</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1057534-866-CM26</t>
+          <t>1057534-867-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21782,12 +21782,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -21797,13 +21797,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>785.72</v>
+        <v>1189.15</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1662-1334-CM26</t>
+          <t>1173430-105-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -21828,12 +21828,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.602.273-3</t>
+          <t>61.950.500-K</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Centro de Educación y Trabajo de Osorno</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>846.59</v>
+        <v>1503.27</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>3201.52</v>
+        <v>3233.58</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>5228.78</v>
+        <v>5255.42</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>2885.62</v>
+        <v>2900.32</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3108.67</v>
+        <v>3120.77</v>
       </c>
     </row>
     <row r="356">
@@ -22163,13 +22163,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3950.11</v>
+        <v>3965.49</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1126922-896-CM26</t>
+          <t>1126922-897-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22189,7 +22189,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -22224,13 +22224,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1701.08</v>
+        <v>2345.89</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1126922-897-CM26</t>
+          <t>1126922-896-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2357.84</v>
+        <v>1692.46</v>
       </c>
     </row>
     <row r="359">
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>840.72</v>
+        <v>846.2</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2306-571-CM26</t>
+          <t>2658-868-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22392,12 +22392,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22407,13 +22407,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>4471.3</v>
+        <v>1385.71</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2306-572-CM26</t>
+          <t>2306-571-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22468,13 +22468,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>7392.65</v>
+        <v>4481.56</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2658-868-CM26</t>
+          <t>2306-572-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -22499,12 +22499,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>9.681.827-0</t>
         </is>
       </c>
       <c r="K362" t="inlineStr"/>
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1382.54</v>
+        <v>7409.6</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>865.13</v>
+        <v>870.92</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>8291.950000000001</v>
+        <v>8347.450000000001</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>4775.83</v>
+        <v>4807.8</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>20270.28</v>
+        <v>20412.14</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2035.46</v>
+        <v>2049.71</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1461.54</v>
+        <v>1456.92</v>
       </c>
     </row>
     <row r="369">
@@ -22956,13 +22956,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2441.43</v>
+        <v>2436.12</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>4195-851-CM26</t>
+          <t>2289-643-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -22982,17 +22982,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.230.200-1</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23002,12 +23002,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -23017,13 +23017,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1254.59</v>
+        <v>774.97</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2289-643-CM26</t>
+          <t>4195-851-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23043,17 +23043,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.230.200-1</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE QUEMCHI</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23063,12 +23063,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K371" t="inlineStr"/>
@@ -23078,13 +23078,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>779.48</v>
+        <v>1247.33</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1126922-962-CM26</t>
+          <t>1063538-4808-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23109,12 +23109,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K372" t="inlineStr"/>
@@ -23139,13 +23139,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1512.51</v>
+        <v>8416.370000000001</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>3888-508-CM26</t>
+          <t>1661-449-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23165,17 +23165,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23185,12 +23185,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -23200,13 +23200,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>879.03</v>
+        <v>873.79</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1057536-2031-CM26</t>
+          <t>1126922-962-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23231,12 +23231,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23246,12 +23246,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>9.681.827-0</t>
         </is>
       </c>
       <c r="K374" t="inlineStr"/>
@@ -23261,13 +23261,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2890.25</v>
+        <v>1488.1</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1063538-4808-CM26</t>
+          <t>2918-35-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23292,12 +23292,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23307,12 +23307,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -23322,13 +23322,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>8554.42</v>
+        <v>780.3200000000001</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1661-449-CM26</t>
+          <t>1057536-2031-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -23353,12 +23353,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23368,12 +23368,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -23383,13 +23383,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>888.12</v>
+        <v>2843.61</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2918-35-CM26</t>
+          <t>3888-508-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -23409,17 +23409,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23429,12 +23429,12 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K377" t="inlineStr"/>
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>793.12</v>
+        <v>864.84</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>927.01</v>
+        <v>912.15</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>771.1900000000001</v>
+        <v>758.8200000000001</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>842.67</v>
+        <v>832.86</v>
       </c>
     </row>
     <row r="381">
@@ -23688,13 +23688,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2858.74</v>
+        <v>2825.48</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1663-980-CM26</t>
+          <t>1057536-2064-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -23714,17 +23714,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -23749,13 +23749,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3407.45</v>
+        <v>1553.63</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1057536-2064-CM26</t>
+          <t>1663-980-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -23775,17 +23775,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>Hospital de Quellón</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1562.29</v>
+        <v>3388.56</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2989-425-CM26</t>
+          <t>1079639-650-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -23841,12 +23841,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23856,12 +23856,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1862.59</v>
+        <v>3535.21</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1079639-650-CM26</t>
+          <t>2989-425-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -23902,12 +23902,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -23917,12 +23917,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>3552.67</v>
+        <v>1853.43</v>
       </c>
     </row>
     <row r="386">
@@ -23993,13 +23993,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1165.18</v>
+        <v>1159.45</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>853-159-CM26</t>
+          <t>853-158-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2670.91</v>
+        <v>5451.25</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>853-158-CM26</t>
+          <t>853-159-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>5415.01</v>
+        <v>2688.79</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,312 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>4236.59</v>
+        <v>4264.95</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>1057539-5492-CM26</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>797.76</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2730-389-CM26</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>69.230.400-4</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>3818.77</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1126922-1120-CM26</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>62.000.800-1</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="n">
+        <v>970.58</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2306-721-CM26</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="n">
+        <v>930.96</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2324-1196-CM26</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="n">
+        <v>1167.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-lagos.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M816"/>
+  <dimension ref="A1:M819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26295,7 +26295,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1224953-31-CM26</t>
+          <t>1224953-30-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26335,12 +26335,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -26354,13 +26354,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1752.96</v>
+        <v>4463.71</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1224953-30-CM26</t>
+          <t>1224953-31-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26400,12 +26400,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -26419,13 +26419,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>4463.71</v>
+        <v>1752.96</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1224953-29-CM26</t>
+          <t>2297-27-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26450,12 +26450,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>71.420.700-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26465,28 +26465,32 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K409" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>3709.59</v>
+        <v>3519.41</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2297-27-CM26</t>
+          <t>1224953-29-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26511,12 +26515,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>71.420.700-8</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26526,26 +26530,22 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>3519.41</v>
+        <v>3709.59</v>
       </c>
     </row>
     <row r="411">
@@ -26933,7 +26933,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>3507-47-CM26</t>
+          <t>2852-21-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -26953,17 +26953,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -26973,12 +26973,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -26992,13 +26992,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>1214.56</v>
+        <v>3217.01</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2852-21-CM26</t>
+          <t>3507-47-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27018,17 +27018,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27038,12 +27038,12 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -27057,7 +27057,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>3217.01</v>
+        <v>1214.56</v>
       </c>
     </row>
     <row r="419">
@@ -27636,7 +27636,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2307-138-CM26</t>
+          <t>1393093-23-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -27676,32 +27676,28 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.668.170-5</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>14278.21</v>
+        <v>75576.67999999999</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1393093-23-CM26</t>
+          <t>2307-138-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -27726,12 +27722,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -27741,28 +27737,32 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
-        </is>
-      </c>
-      <c r="K429" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>75576.67999999999</v>
+        <v>14278.21</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>3202-18-CM26</t>
+          <t>4625-5-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -27787,12 +27787,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>61.102.120-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -27821,13 +27821,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>3995.78</v>
+        <v>2396.77</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>4625-5-CM26</t>
+          <t>3202-18-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -27852,12 +27852,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.102.120-8</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -27886,7 +27886,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>2396.77</v>
+        <v>3995.78</v>
       </c>
     </row>
     <row r="432">
@@ -28587,7 +28587,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>3510-68-CM26</t>
+          <t>2297-94-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -28607,17 +28607,17 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -28627,12 +28627,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -28646,13 +28646,13 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>1620.67</v>
+        <v>10285.19</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2297-94-CM26</t>
+          <t>3289-8-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -28672,17 +28672,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -28692,12 +28692,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -28711,13 +28711,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>10285.19</v>
+        <v>2975.66</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>3289-8-CM26</t>
+          <t>3510-68-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -28742,12 +28742,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -28757,12 +28757,12 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -28776,7 +28776,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2975.66</v>
+        <v>1620.67</v>
       </c>
     </row>
     <row r="446">
@@ -29107,7 +29107,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1057539-833-CM26</t>
+          <t>2289-197-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -29127,17 +29127,17 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -29147,12 +29147,12 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -29166,13 +29166,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>24938.21</v>
+        <v>6846.96</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2289-197-CM26</t>
+          <t>1057539-833-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29192,17 +29192,17 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -29212,12 +29212,12 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
@@ -29231,13 +29231,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>6846.96</v>
+        <v>24938.21</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1161-63-CM26</t>
+          <t>3878-6-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29262,12 +29262,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.231.200-7</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE FUTALEUFU</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -29277,32 +29277,28 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K453" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>953.0599999999999</v>
+        <v>3642.59</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>3878-6-CM26</t>
+          <t>3510-104-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29327,12 +29323,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>69.231.200-7</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTALEUFU</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29342,28 +29338,32 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K454" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>3642.59</v>
+        <v>6233.58</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>3510-104-CM26</t>
+          <t>1161-63-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29388,12 +29388,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29403,12 +29403,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
@@ -29422,13 +29422,13 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>6233.58</v>
+        <v>953.0599999999999</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>3510-112-CM26</t>
+          <t>1057536-445-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -29453,12 +29453,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -29468,17 +29468,17 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -29487,13 +29487,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>954.04</v>
+        <v>2414.89</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1057536-445-CM26</t>
+          <t>1057536-446-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -29533,32 +29533,28 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K457" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>79.668.170-5</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr"/>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2414.89</v>
+        <v>814.67</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1057536-446-CM26</t>
+          <t>3510-112-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -29583,12 +29579,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -29598,22 +29594,26 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
-        </is>
-      </c>
-      <c r="K458" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>814.67</v>
+        <v>954.04</v>
       </c>
     </row>
     <row r="459">
@@ -29814,7 +29814,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>387-121-CM26</t>
+          <t>4906-42-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -29839,12 +29839,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.980.740-5</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -29854,12 +29854,12 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -29873,13 +29873,13 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>3498.85</v>
+        <v>1762.28</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>4906-42-CM26</t>
+          <t>387-121-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -29904,12 +29904,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>61.980.740-5</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -29938,7 +29938,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1762.28</v>
+        <v>3498.85</v>
       </c>
     </row>
     <row r="464">
@@ -30070,7 +30070,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2886-21-CM26</t>
+          <t>2886-20-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30110,12 +30110,12 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>79.668.170-5</t>
         </is>
       </c>
       <c r="K466" t="inlineStr"/>
@@ -30125,13 +30125,13 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1479.03</v>
+        <v>872.74</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2886-20-CM26</t>
+          <t>2886-21-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30171,12 +30171,12 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K467" t="inlineStr"/>
@@ -30186,7 +30186,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>872.74</v>
+        <v>1479.03</v>
       </c>
     </row>
     <row r="468">
@@ -30452,7 +30452,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2328-150-CM26</t>
+          <t>2328-149-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -30492,28 +30492,32 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K472" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>3038.37</v>
+        <v>3085.43</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1224974-32-CM26</t>
+          <t>2137-161-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -30533,17 +30537,17 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>65.137.070-1</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE OSORNO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -30572,13 +30576,13 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>814.38</v>
+        <v>1237.62</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2137-161-CM26</t>
+          <t>1224974-32-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -30598,17 +30602,17 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>65.137.070-1</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>CORP CULTURAL DE OSORNO</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -30637,13 +30641,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1237.62</v>
+        <v>814.38</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2328-149-CM26</t>
+          <t>2328-150-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -30683,26 +30687,22 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K475" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>3085.43</v>
+        <v>3038.37</v>
       </c>
     </row>
     <row r="476">
@@ -30964,7 +30964,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>162-74-CM26</t>
+          <t>437-13-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -30989,12 +30989,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -31004,12 +31004,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -31023,13 +31023,13 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>1072</v>
+        <v>2262.59</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>437-12-CM26</t>
+          <t>162-74-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31049,17 +31049,17 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -31069,12 +31069,12 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
@@ -31088,13 +31088,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1135.98</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>437-13-CM26</t>
+          <t>437-12-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -31134,12 +31134,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
@@ -31153,7 +31153,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2262.59</v>
+        <v>1135.98</v>
       </c>
     </row>
     <row r="483">
@@ -31549,7 +31549,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>3510-204-CM26</t>
+          <t>2306-76-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -31569,17 +31569,17 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -31589,12 +31589,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
@@ -31608,13 +31608,13 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1561.93</v>
+        <v>5120.73</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2306-76-CM26</t>
+          <t>2306-69-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -31654,17 +31654,17 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -31673,13 +31673,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>5120.73</v>
+        <v>1591.54</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1663-193-CM26</t>
+          <t>2887-44-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -31699,17 +31699,17 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -31719,26 +31719,22 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K491" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.668.170-5</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>3042.66</v>
+        <v>918.21</v>
       </c>
     </row>
     <row r="492">
@@ -31805,7 +31801,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2306-69-CM26</t>
+          <t>2887-46-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -31830,12 +31826,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -31845,17 +31841,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -31864,13 +31860,13 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1591.54</v>
+        <v>768.21</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2887-46-CM26</t>
+          <t>2306-71-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -31895,12 +31891,12 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -31929,13 +31925,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>768.21</v>
+        <v>2961.85</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2306-71-CM26</t>
+          <t>1663-193-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -31955,17 +31951,17 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -31975,12 +31971,12 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
@@ -31994,13 +31990,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>2961.85</v>
+        <v>3042.66</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2887-44-CM26</t>
+          <t>3510-204-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32020,17 +32016,17 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -32040,28 +32036,32 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
-        </is>
-      </c>
-      <c r="K496" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>918.21</v>
+        <v>1561.93</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>545598-141-CM26</t>
+          <t>4195-284-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>69.230.200-1</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>I MUNICIPALIDAD DE QUEMCHI</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32101,12 +32101,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -32120,13 +32120,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>5042.96</v>
+        <v>1211.25</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4195-284-CM26</t>
+          <t>545598-141-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32151,12 +32151,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>69.230.200-1</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -32166,12 +32166,12 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
@@ -32185,7 +32185,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1211.25</v>
+        <v>5042.96</v>
       </c>
     </row>
     <row r="499">
@@ -32256,7 +32256,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2095-10-CM26</t>
+          <t>1663-215-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32281,12 +32281,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -32296,17 +32296,17 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -32315,13 +32315,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1757.55</v>
+        <v>1002.64</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2306-86-CM26</t>
+          <t>1663-218-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32341,17 +32341,17 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -32380,13 +32380,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>19368.03</v>
+        <v>4701.13</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2306-84-CM26</t>
+          <t>2095-10-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32406,17 +32406,17 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -32445,13 +32445,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>13409.56</v>
+        <v>1757.55</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1663-218-CM26</t>
+          <t>2306-84-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -32471,17 +32471,17 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -32491,12 +32491,12 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
@@ -32510,13 +32510,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>4701.13</v>
+        <v>13409.56</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1663-215-CM26</t>
+          <t>2306-86-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -32536,17 +32536,17 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -32556,17 +32556,17 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -32575,7 +32575,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1002.64</v>
+        <v>19368.03</v>
       </c>
     </row>
     <row r="505">
@@ -32772,7 +32772,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1413-215-CM26</t>
+          <t>3888-189-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -32792,17 +32792,17 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>61.004.098-5</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -32812,12 +32812,12 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
@@ -32831,7 +32831,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>4603.45</v>
+        <v>1193.16</v>
       </c>
     </row>
     <row r="509">
@@ -32902,7 +32902,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>3888-189-CM26</t>
+          <t>1413-215-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -32922,17 +32922,17 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>61.004.098-5</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -32942,12 +32942,12 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -32961,7 +32961,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>1193.16</v>
+        <v>4603.45</v>
       </c>
     </row>
     <row r="511">
@@ -33093,7 +33093,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>5110-87-CM26</t>
+          <t>3289-24-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33113,17 +33113,17 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -33133,17 +33133,17 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -33152,13 +33152,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2619.84</v>
+        <v>950.5599999999999</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>3289-24-CM26</t>
+          <t>1224953-185-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33178,17 +33178,17 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>71.420.700-8</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -33198,17 +33198,17 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -33217,13 +33217,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>950.5599999999999</v>
+        <v>3162.44</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>4180-48-CM26</t>
+          <t>5110-87-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33243,17 +33243,17 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -33263,12 +33263,12 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
@@ -33282,13 +33282,13 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>3177.88</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>1224953-185-CM26</t>
+          <t>4180-48-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33308,17 +33308,17 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>71.420.700-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -33328,12 +33328,12 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
@@ -33347,7 +33347,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>3162.44</v>
+        <v>3177.88</v>
       </c>
     </row>
     <row r="517">
@@ -33865,7 +33865,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1079639-202-CM26</t>
+          <t>2324-411-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -33890,12 +33890,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -33905,12 +33905,12 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
@@ -33924,13 +33924,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>3279.92</v>
+        <v>1355.79</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2324-411-CM26</t>
+          <t>1079639-202-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -33955,12 +33955,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -33970,12 +33970,12 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -33989,13 +33989,13 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1355.79</v>
+        <v>3279.92</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2324-426-CM26</t>
+          <t>3481-39-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34020,12 +34020,12 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -34035,28 +34035,32 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K527" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>1724.64</v>
+        <v>853.5700000000001</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>3481-39-CM26</t>
+          <t>2324-426-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34081,12 +34085,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34096,26 +34100,22 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K528" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>853.5700000000001</v>
+        <v>1724.64</v>
       </c>
     </row>
     <row r="529">
@@ -34373,7 +34373,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2989-178-CM26</t>
+          <t>2989-179-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -34413,32 +34413,28 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K533" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2901.04</v>
+        <v>775.16</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2989-179-CM26</t>
+          <t>1661-198-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -34463,12 +34459,12 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -34478,28 +34474,32 @@
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K534" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>775.16</v>
+        <v>871.04</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>1661-198-CM26</t>
+          <t>2989-178-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -34524,12 +34524,12 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -34539,12 +34539,12 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
@@ -34558,7 +34558,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>871.04</v>
+        <v>2901.04</v>
       </c>
     </row>
     <row r="536">
@@ -35596,7 +35596,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>707425-74-CM26</t>
+          <t>1057539-2635-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -35616,17 +35616,17 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -35655,13 +35655,13 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1208.98</v>
+        <v>859.3200000000001</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2306-196-CM26</t>
+          <t>2730-176-CM26</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -35681,17 +35681,17 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -35701,32 +35701,28 @@
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K553" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr"/>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>1209.06</v>
+        <v>948.3200000000001</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>1057539-2635-CM26</t>
+          <t>707425-74-CM26</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -35746,17 +35742,17 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -35785,13 +35781,13 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>859.3200000000001</v>
+        <v>1208.98</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2730-176-CM26</t>
+          <t>2306-196-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -35811,17 +35807,17 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -35831,22 +35827,26 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K555" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>948.3200000000001</v>
+        <v>1209.06</v>
       </c>
     </row>
     <row r="556">
@@ -36108,7 +36108,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>162-128-CM26</t>
+          <t>4042-88-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -36128,17 +36128,17 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.220.402-6</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -36148,12 +36148,12 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
@@ -36167,13 +36167,13 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>794.09</v>
+        <v>3870.72</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>162-131-CM26</t>
+          <t>162-128-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36232,13 +36232,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>784.7</v>
+        <v>794.09</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>853-84-CM26</t>
+          <t>162-131-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36263,12 +36263,12 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -36278,12 +36278,12 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
@@ -36297,13 +36297,13 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>9371.26</v>
+        <v>784.7</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>752-102-CM26</t>
+          <t>853-84-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36328,12 +36328,12 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -36343,12 +36343,12 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -36362,13 +36362,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>784.41</v>
+        <v>9371.26</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>1063538-3318-CM26</t>
+          <t>752-102-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -36393,12 +36393,12 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -36408,28 +36408,32 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K564" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>6176.66</v>
+        <v>784.41</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>4042-88-CM26</t>
+          <t>1063538-3318-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -36449,17 +36453,17 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>69.220.402-6</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRESIA</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -36469,26 +36473,22 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K565" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>3870.72</v>
+        <v>6176.66</v>
       </c>
     </row>
     <row r="566">
@@ -36624,7 +36624,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>1518-7-CM26</t>
+          <t>1428662-47-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -36644,17 +36644,17 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>61.818.004-2</t>
+          <t>71.160.900-8</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>CORP MUNICIPAL DE PUQUELDON PARA LA EDUC</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -36664,17 +36664,17 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
@@ -36683,13 +36683,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>986.09</v>
+        <v>1808.13</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>1428662-47-CM26</t>
+          <t>2048-1200-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -36709,17 +36709,17 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>71.160.900-8</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUQUELDON PARA LA EDUC</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -36729,12 +36729,12 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
@@ -36748,13 +36748,13 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>1808.13</v>
+        <v>3018.32</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2048-1200-CM26</t>
+          <t>1428662-46-CM26</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -36774,17 +36774,17 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>71.160.900-8</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>CORP MUNICIPAL DE PUQUELDON PARA LA EDUC</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -36794,32 +36794,28 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K570" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>3018.32</v>
+        <v>1186.12</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>1428662-46-CM26</t>
+          <t>1518-7-CM26</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -36839,17 +36835,17 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>71.160.900-8</t>
+          <t>61.818.004-2</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUQUELDON PARA LA EDUC</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -36859,22 +36855,26 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K571" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>1186.12</v>
+        <v>986.09</v>
       </c>
     </row>
     <row r="572">
@@ -36945,7 +36945,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>162-165-CM26</t>
+          <t>1740-16-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -36970,12 +36970,12 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -36985,26 +36985,22 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K573" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr"/>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1145.09</v>
+        <v>783.34</v>
       </c>
     </row>
     <row r="574">
@@ -37140,7 +37136,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>1740-16-CM26</t>
+          <t>162-165-CM26</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -37165,12 +37161,12 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -37180,22 +37176,26 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K576" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>783.34</v>
+        <v>1145.09</v>
       </c>
     </row>
     <row r="577">
@@ -37266,7 +37266,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>1126922-510-CM26</t>
+          <t>3508-414-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37286,17 +37286,17 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.230.500-0</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE CHONCHI</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -37306,12 +37306,12 @@
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
@@ -37325,13 +37325,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>1035.82</v>
+        <v>2755.31</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1057534-554-CM26</t>
+          <t>1057534-555-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -37371,32 +37371,28 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K579" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr"/>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>870.42</v>
+        <v>810.5599999999999</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>1057534-555-CM26</t>
+          <t>2306-273-CM26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -37416,17 +37412,17 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -37436,12 +37432,12 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K580" t="inlineStr"/>
@@ -37451,13 +37447,13 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>810.5599999999999</v>
+        <v>2518.98</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>3508-414-CM26</t>
+          <t>1126922-510-CM26</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -37477,17 +37473,17 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>69.230.500-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHONCHI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -37497,12 +37493,12 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K581" t="inlineStr">
@@ -37516,13 +37512,13 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2755.31</v>
+        <v>1035.82</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2306-273-CM26</t>
+          <t>1057534-554-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -37542,17 +37538,17 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -37562,22 +37558,26 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
-        </is>
-      </c>
-      <c r="K582" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>2518.98</v>
+        <v>870.42</v>
       </c>
     </row>
     <row r="583">
@@ -37648,7 +37648,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>450-159-CM26</t>
+          <t>2297-603-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -37673,12 +37673,12 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>69.210.300-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -37688,12 +37688,12 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
@@ -37707,13 +37707,13 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>3308.56</v>
+        <v>5903.68</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2297-603-CM26</t>
+          <t>450-159-CM26</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -37738,12 +37738,12 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.210.300-9</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -37753,12 +37753,12 @@
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K585" t="inlineStr">
@@ -37772,7 +37772,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>5903.68</v>
+        <v>3308.56</v>
       </c>
     </row>
     <row r="586">
@@ -37843,7 +37843,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>1126922-554-CM26</t>
+          <t>2306-302-CM26</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -37863,17 +37863,17 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -37902,13 +37902,13 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>954.79</v>
+        <v>4831.3</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2136-310-CM26</t>
+          <t>1126922-554-CM26</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -37933,12 +37933,12 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>61.602.270-9</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -37967,13 +37967,13 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>782.76</v>
+        <v>954.79</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2306-302-CM26</t>
+          <t>2136-310-CM26</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -37993,17 +37993,17 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.602.270-9</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -38032,7 +38032,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>4831.3</v>
+        <v>782.76</v>
       </c>
     </row>
     <row r="590">
@@ -38103,7 +38103,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2306-308-CM26</t>
+          <t>2306-301-CM26</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -38162,13 +38162,13 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>2700.97</v>
+        <v>4040.62</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2306-301-CM26</t>
+          <t>2306-308-CM26</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -38227,13 +38227,13 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>4040.62</v>
+        <v>2700.97</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2307-543-CM26</t>
+          <t>3479-800-CM26</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38258,12 +38258,12 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -38273,28 +38273,32 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K593" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>4446.49</v>
+        <v>817.11</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2307-544-CM26</t>
+          <t>2307-543-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -38334,32 +38338,28 @@
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K594" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr"/>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>1535.7</v>
+        <v>4446.49</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2059-229-CM26</t>
+          <t>2307-544-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -38384,12 +38384,12 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>61.602.261-k</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO OCTAY</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -38418,13 +38418,13 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2597.56</v>
+        <v>1535.7</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>3479-800-CM26</t>
+          <t>2059-229-CM26</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -38449,12 +38449,12 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>61.602.261-k</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO OCTAY</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -38483,7 +38483,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>817.11</v>
+        <v>2597.56</v>
       </c>
     </row>
     <row r="597">
@@ -38619,7 +38619,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2306-341-CM26</t>
+          <t>1057539-3519-CM26</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -38644,12 +38644,12 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -38659,22 +38659,26 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
-        </is>
-      </c>
-      <c r="K599" t="inlineStr"/>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>8716.16</v>
+        <v>17167.25</v>
       </c>
     </row>
     <row r="600">
@@ -38810,7 +38814,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1057539-3519-CM26</t>
+          <t>2306-341-CM26</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -38835,12 +38839,12 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -38850,26 +38854,22 @@
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K602" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>17167.25</v>
+        <v>8716.16</v>
       </c>
     </row>
     <row r="603">
@@ -39001,7 +39001,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2324-689-CM26</t>
+          <t>1063538-3954-CM26</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -39021,17 +39021,17 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -39041,12 +39041,12 @@
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K605" t="inlineStr"/>
@@ -39056,13 +39056,13 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2006.57</v>
+        <v>7357.07</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>1063538-3954-CM26</t>
+          <t>2289-519-CM26</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -39087,12 +39087,12 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -39102,28 +39102,32 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K606" t="inlineStr"/>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>7357.07</v>
+        <v>1337.58</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2289-519-CM26</t>
+          <t>2324-689-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -39143,17 +39147,17 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -39163,26 +39167,22 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
-        </is>
-      </c>
-      <c r="K607" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.668.170-5</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1337.58</v>
+        <v>2006.57</v>
       </c>
     </row>
     <row r="608">
@@ -39639,7 +39639,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2306-431-CM26</t>
+          <t>1057539-4101-CM26</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -39664,12 +39664,12 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -39679,28 +39679,32 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
-        </is>
-      </c>
-      <c r="K615" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>5409.88</v>
+        <v>3775.2</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>4906-134-CM26</t>
+          <t>2730-279-CM26</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -39725,12 +39729,12 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>61.980.740-5</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -39740,32 +39744,28 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K616" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr"/>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>961.34</v>
+        <v>3050.92</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2730-279-CM26</t>
+          <t>1057536-1565-CM26</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -39790,12 +39790,12 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -39805,28 +39805,32 @@
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K617" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>3050.92</v>
+        <v>1713.69</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>1057539-4102-CM26</t>
+          <t>4906-134-CM26</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -39851,12 +39855,12 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.980.740-5</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -39866,28 +39870,32 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K618" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>1211.89</v>
+        <v>961.34</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>1057536-1565-CM26</t>
+          <t>2306-431-CM26</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -39912,12 +39920,12 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -39927,32 +39935,28 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K619" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr"/>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>1713.69</v>
+        <v>5409.88</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>1057539-4101-CM26</t>
+          <t>1057539-4102-CM26</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -39992,32 +39996,28 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K620" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr"/>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>3775.2</v>
+        <v>1211.89</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>1126922-709-CM26</t>
+          <t>1057539-4149-CM26</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -40042,12 +40042,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -40057,28 +40057,32 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
-        </is>
-      </c>
-      <c r="K621" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>1144.37</v>
+        <v>1483.66</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>1126922-711-CM26</t>
+          <t>1057539-4150-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -40103,12 +40107,12 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -40118,28 +40122,32 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
-        </is>
-      </c>
-      <c r="K622" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>1142.79</v>
+        <v>1320.95</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>1057539-4150-CM26</t>
+          <t>1663-591-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -40164,12 +40172,12 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -40179,12 +40187,12 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
@@ -40198,13 +40206,13 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>1320.95</v>
+        <v>2863.06</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>1057539-4149-CM26</t>
+          <t>1126922-709-CM26</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -40229,12 +40237,12 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -40244,32 +40252,28 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K624" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1483.66</v>
+        <v>1144.37</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>1663-591-CM26</t>
+          <t>1126922-711-CM26</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -40294,12 +40298,12 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -40309,26 +40313,22 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K625" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>2863.06</v>
+        <v>1142.79</v>
       </c>
     </row>
     <row r="626">
@@ -40846,7 +40846,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2306-349-CM26</t>
+          <t>2306-420-CM26</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -40905,13 +40905,13 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>4464.32</v>
+        <v>5805.07</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2306-420-CM26</t>
+          <t>2306-349-CM26</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -40970,7 +40970,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>5805.07</v>
+        <v>4464.32</v>
       </c>
     </row>
     <row r="636">
@@ -41102,7 +41102,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2324-832-CM26</t>
+          <t>2324-831-CM26</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -41142,12 +41142,12 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K638" t="inlineStr"/>
@@ -41157,13 +41157,13 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>2446.08</v>
+        <v>1617.58</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2324-831-CM26</t>
+          <t>2324-832-CM26</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -41203,12 +41203,12 @@
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K639" t="inlineStr"/>
@@ -41218,13 +41218,13 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>1617.58</v>
+        <v>2446.08</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2137-504-CM26</t>
+          <t>387-369-CM26</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -41249,12 +41249,12 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -41264,12 +41264,12 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
@@ -41283,7 +41283,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>850.77</v>
+        <v>2528.4</v>
       </c>
     </row>
     <row r="641">
@@ -41354,7 +41354,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>387-369-CM26</t>
+          <t>2137-504-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -41379,12 +41379,12 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -41394,12 +41394,12 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
@@ -41413,7 +41413,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>2528.4</v>
+        <v>850.77</v>
       </c>
     </row>
     <row r="643">
@@ -41606,7 +41606,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>853-119-CM26</t>
+          <t>853-120-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -41665,13 +41665,13 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>22296.4</v>
+        <v>10931.62</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>853-120-CM26</t>
+          <t>853-119-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -41730,7 +41730,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>10931.62</v>
+        <v>22296.4</v>
       </c>
     </row>
     <row r="648">
@@ -42321,7 +42321,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>1057534-866-CM26</t>
+          <t>1057534-867-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -42361,28 +42361,32 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K657" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>793.63</v>
+        <v>1189.15</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>1057534-867-CM26</t>
+          <t>1173430-105-CM26</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -42407,12 +42411,12 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.950.500-K</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -42422,12 +42426,12 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
@@ -42441,13 +42445,13 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>1189.15</v>
+        <v>1503.27</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>1173430-105-CM26</t>
+          <t>1057534-866-CM26</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -42472,12 +42476,12 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>61.950.500-K</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -42487,26 +42491,22 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K659" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr"/>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1503.27</v>
+        <v>793.63</v>
       </c>
     </row>
     <row r="660">
@@ -42577,7 +42577,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2328-667-CM26</t>
+          <t>2328-648-CM26</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -42617,12 +42617,12 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K661" t="inlineStr"/>
@@ -42632,13 +42632,13 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>2900.32</v>
+        <v>5255.42</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2328-648-CM26</t>
+          <t>2328-667-CM26</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -42678,12 +42678,12 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>79.668.170-5</t>
         </is>
       </c>
       <c r="K662" t="inlineStr"/>
@@ -42693,13 +42693,13 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>5255.42</v>
+        <v>2900.32</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2852-650-CM26</t>
+          <t>2324-902-CM26</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -42739,12 +42739,12 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
@@ -42758,13 +42758,13 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>3965.49</v>
+        <v>3120.77</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2324-902-CM26</t>
+          <t>2852-650-CM26</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -42789,12 +42789,12 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -42804,12 +42804,12 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
@@ -42823,13 +42823,13 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>3120.77</v>
+        <v>3965.49</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>1126922-897-CM26</t>
+          <t>1126922-896-CM26</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -42884,13 +42884,13 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2345.89</v>
+        <v>1692.46</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>1126922-896-CM26</t>
+          <t>1126922-897-CM26</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -42945,7 +42945,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>1692.46</v>
+        <v>2345.89</v>
       </c>
     </row>
     <row r="667">
@@ -43012,7 +43012,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2306-571-CM26</t>
+          <t>2306-572-CM26</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -43067,7 +43067,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>4481.56</v>
+        <v>7409.6</v>
       </c>
     </row>
     <row r="669">
@@ -43138,7 +43138,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2306-572-CM26</t>
+          <t>2306-571-CM26</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -43193,13 +43193,13 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>7409.6</v>
+        <v>4481.56</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2328-839-CM26</t>
+          <t>2328-826-CM26</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -43239,26 +43239,22 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K671" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.668.170-5</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr"/>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>4807.8</v>
+        <v>870.92</v>
       </c>
     </row>
     <row r="672">
@@ -43325,7 +43321,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2328-826-CM26</t>
+          <t>2328-839-CM26</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -43365,22 +43361,26 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
-        </is>
-      </c>
-      <c r="K673" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>870.92</v>
+        <v>4807.8</v>
       </c>
     </row>
     <row r="674">
@@ -43833,7 +43833,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>3888-508-CM26</t>
+          <t>1661-449-CM26</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -43853,17 +43853,17 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -43873,12 +43873,12 @@
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
@@ -43892,13 +43892,13 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>864.84</v>
+        <v>873.79</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>1661-449-CM26</t>
+          <t>1126922-962-CM26</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -43923,12 +43923,12 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -43938,26 +43938,22 @@
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K682" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>873.79</v>
+        <v>1488.1</v>
       </c>
     </row>
     <row r="683">
@@ -44028,7 +44024,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>1126922-962-CM26</t>
+          <t>1057536-2031-CM26</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -44053,12 +44049,12 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -44068,28 +44064,32 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
-        </is>
-      </c>
-      <c r="K684" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>1488.1</v>
+        <v>2843.61</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>1057536-2031-CM26</t>
+          <t>3888-508-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -44109,17 +44109,17 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -44129,12 +44129,12 @@
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
@@ -44148,7 +44148,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>2843.61</v>
+        <v>864.84</v>
       </c>
     </row>
     <row r="686">
@@ -44544,7 +44544,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>1079639-650-CM26</t>
+          <t>2324-1021-CM26</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -44569,12 +44569,12 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -44584,12 +44584,12 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
@@ -44603,13 +44603,13 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>3535.21</v>
+        <v>1159.45</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2989-425-CM26</t>
+          <t>1079639-650-CM26</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -44634,12 +44634,12 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -44649,12 +44649,12 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -44668,13 +44668,13 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>1853.43</v>
+        <v>3535.21</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2324-1021-CM26</t>
+          <t>2989-425-CM26</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -44699,12 +44699,12 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -44733,13 +44733,13 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>1159.45</v>
+        <v>1853.43</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>853-158-CM26</t>
+          <t>2297-995-CM26</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -44759,17 +44759,17 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -44779,12 +44779,12 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>5451.25</v>
+        <v>4264.95</v>
       </c>
     </row>
     <row r="696">
@@ -44869,7 +44869,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2297-995-CM26</t>
+          <t>853-158-CM26</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -44889,17 +44889,17 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -44909,12 +44909,12 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
@@ -44928,13 +44928,13 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>4264.95</v>
+        <v>5451.25</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2328-945-CM26</t>
+          <t>2328-944-CM26</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -44974,32 +44974,28 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA ABSA LIMITADA</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K698" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.668.170-5</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr"/>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>944.78</v>
+        <v>812.63</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>1057539-5491-CM26</t>
+          <t>2328-945-CM26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -45024,12 +45020,12 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -45039,12 +45035,12 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
@@ -45058,7 +45054,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>1351.16</v>
+        <v>944.78</v>
       </c>
     </row>
     <row r="700">
@@ -45129,7 +45125,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2328-944-CM26</t>
+          <t>1057539-5491-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45154,12 +45150,12 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -45169,22 +45165,26 @@
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ABSA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>79.668.170-5</t>
-        </is>
-      </c>
-      <c r="K701" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>812.63</v>
+        <v>1351.16</v>
       </c>
     </row>
     <row r="702">
@@ -45629,7 +45629,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1057535-400-CM26</t>
+          <t>1413-754-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -45654,12 +45654,12 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>61.980.070-2</t>
+          <t>61.004.098-5</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>HOSPITAL FUTA SRÜKA LAWENCHE KUNKO MAPU MO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -45688,13 +45688,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1947.68</v>
+        <v>3949.04</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2306-641-CM26</t>
+          <t>1057535-400-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -45714,17 +45714,17 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.980.070-2</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>HOSPITAL FUTA SRÜKA LAWENCHE KUNKO MAPU MO</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -45753,13 +45753,13 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>4171.94</v>
+        <v>1947.68</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>1413-754-CM26</t>
+          <t>2306-641-CM26</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -45779,17 +45779,17 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>61.004.098-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -45818,7 +45818,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>3949.04</v>
+        <v>4171.94</v>
       </c>
     </row>
     <row r="712">
@@ -46137,7 +46137,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>1057539-5490-CM26</t>
+          <t>1127-119-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -46162,12 +46162,12 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -46196,13 +46196,13 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>1494.67</v>
+        <v>3979.43</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>1127-119-CM26</t>
+          <t>1057539-5490-CM26</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -46227,12 +46227,12 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -46261,7 +46261,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>3979.43</v>
+        <v>1494.67</v>
       </c>
     </row>
     <row r="719">
@@ -46848,7 +46848,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2941-253-CM26</t>
+          <t>3507-564-CM26</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -46873,12 +46873,12 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>69.210.200-2</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PABLO</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -46888,12 +46888,12 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
@@ -46907,13 +46907,13 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>789.64</v>
+        <v>3545.72</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>3897-462-CM26</t>
+          <t>3507-565-CM26</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -46933,17 +46933,17 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>69.231.200-7</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTALEUFU</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -46953,17 +46953,17 @@
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
@@ -46972,13 +46972,13 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2115.49</v>
+        <v>1286.69</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>3507-564-CM26</t>
+          <t>1126922-1196-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -46998,17 +46998,17 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -47018,12 +47018,12 @@
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
@@ -47037,13 +47037,13 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>3545.72</v>
+        <v>796.58</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>3507-565-CM26</t>
+          <t>3897-462-CM26</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -47063,17 +47063,17 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.231.200-7</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE FUTALEUFU</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -47083,17 +47083,17 @@
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
@@ -47102,13 +47102,13 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>1286.69</v>
+        <v>2115.49</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>1126922-1196-CM26</t>
+          <t>2941-253-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -47128,17 +47128,17 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.210.200-2</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -47148,12 +47148,12 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
@@ -47167,7 +47167,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>796.58</v>
+        <v>789.64</v>
       </c>
     </row>
     <row r="733">
@@ -47368,7 +47368,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>437-63-CM26</t>
+          <t>2328-1138-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -47388,17 +47388,17 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -47408,17 +47408,17 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
@@ -47427,13 +47427,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>2190.76</v>
+        <v>1111.62</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2328-1138-CM26</t>
+          <t>437-63-CM26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -47453,17 +47453,17 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -47473,17 +47473,17 @@
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
@@ -47492,7 +47492,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>1111.62</v>
+        <v>2190.76</v>
       </c>
     </row>
     <row r="738">
@@ -48014,7 +48014,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2730-468-CM26</t>
+          <t>2324-1233-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -48039,12 +48039,12 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -48054,17 +48054,17 @@
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
@@ -48073,13 +48073,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>3803.74</v>
+        <v>3587.05</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2324-1233-CM26</t>
+          <t>2730-468-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -48104,12 +48104,12 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -48119,17 +48119,17 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
@@ -48138,13 +48138,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>3587.05</v>
+        <v>3803.74</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>1063538-6326-CM26</t>
+          <t>2730-467-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -48164,17 +48164,17 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -48199,7 +48199,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>7192.94</v>
+        <v>1273.99</v>
       </c>
     </row>
     <row r="749">
@@ -48335,7 +48335,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2730-467-CM26</t>
+          <t>1063538-6326-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -48355,17 +48355,17 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -48390,7 +48390,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>1273.99</v>
+        <v>7192.94</v>
       </c>
     </row>
     <row r="752">
@@ -50009,7 +50009,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>4834-294-CM26</t>
+          <t>2306-856-CM26</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -50034,12 +50034,12 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>61.932.200-2</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -50049,12 +50049,12 @@
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K777" t="inlineStr">
@@ -50068,13 +50068,13 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>938.87</v>
+        <v>1700.35</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2306-856-CM26</t>
+          <t>4834-294-CM26</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -50099,12 +50099,12 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.932.200-2</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -50114,12 +50114,12 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
@@ -50133,7 +50133,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>1700.35</v>
+        <v>938.87</v>
       </c>
     </row>
     <row r="779">
@@ -50330,7 +50330,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>1057534-1314-CM26</t>
+          <t>2332-1144-CM26</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -50355,12 +50355,12 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -50370,28 +50370,32 @@
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K782" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>795.15</v>
+        <v>9301.41</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2306-860-CM26</t>
+          <t>2730-551-CM26</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -50411,17 +50415,17 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -50431,12 +50435,12 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K783" t="inlineStr"/>
@@ -50446,13 +50450,13 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>1004.79</v>
+        <v>3827.08</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>3897-536-CM26</t>
+          <t>2306-860-CM26</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -50477,12 +50481,12 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>69.231.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTALEUFU</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -50492,32 +50496,28 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K784" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr"/>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>2009.4</v>
+        <v>1004.79</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2332-1144-CM26</t>
+          <t>1057534-1314-CM26</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -50542,12 +50542,12 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -50557,32 +50557,28 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K785" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr"/>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>9301.41</v>
+        <v>795.15</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2730-551-CM26</t>
+          <t>3897-536-CM26</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -50602,17 +50598,17 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>69.231.200-7</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>I MUNICIPALIDAD DE FUTALEUFU</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -50622,28 +50618,32 @@
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K786" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>3827.08</v>
+        <v>2009.4</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>1057539-8210-CM26</t>
+          <t>656-198-CM26</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -50668,12 +50668,12 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.818.001-8</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -50683,17 +50683,17 @@
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K787" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L787" t="inlineStr">
@@ -50702,7 +50702,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>20010.15</v>
+        <v>1486.74</v>
       </c>
     </row>
     <row r="788">
@@ -50773,7 +50773,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>656-198-CM26</t>
+          <t>1057539-8210-CM26</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -50798,12 +50798,12 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>61.818.001-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -50813,17 +50813,17 @@
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K789" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L789" t="inlineStr">
@@ -50832,7 +50832,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>1486.74</v>
+        <v>20010.15</v>
       </c>
     </row>
     <row r="790">
@@ -51033,7 +51033,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2324-1404-CM26</t>
+          <t>1063538-7277-CM26</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -51058,12 +51058,12 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -51088,13 +51088,13 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>1007.87</v>
+        <v>6222.95</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>1063538-7277-CM26</t>
+          <t>2324-1404-CM26</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -51119,12 +51119,12 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
@@ -51149,7 +51149,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>6222.95</v>
+        <v>1007.87</v>
       </c>
     </row>
     <row r="795">
@@ -51281,7 +51281,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>1057539-8459-CM26</t>
+          <t>3510-931-CM26</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -51306,12 +51306,12 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.220.601-0</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
@@ -51321,28 +51321,32 @@
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K797" t="inlineStr"/>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L797" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>1596.17</v>
+        <v>1640.54</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>1057539-8462-CM26</t>
+          <t>1456840-68-CM26</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -51362,17 +51366,17 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
@@ -51382,12 +51386,12 @@
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K798" t="inlineStr">
@@ -51401,13 +51405,13 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>794.66</v>
+        <v>874.97</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>1456840-68-CM26</t>
+          <t>1057539-8459-CM26</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -51432,12 +51436,12 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
@@ -51447,32 +51451,28 @@
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K799" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.307.160-6</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr"/>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>874.97</v>
+        <v>1596.17</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>3510-931-CM26</t>
+          <t>1057539-8452-CM26</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -51492,17 +51492,17 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>69.220.601-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
@@ -51512,17 +51512,17 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L800" t="inlineStr">
@@ -51531,13 +51531,13 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>1640.54</v>
+        <v>2988.96</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>1057539-8452-CM26</t>
+          <t>1057539-8462-CM26</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -51577,17 +51577,17 @@
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K801" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L801" t="inlineStr">
@@ -51596,13 +51596,13 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>2988.96</v>
+        <v>794.66</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>1810-45-CM26</t>
+          <t>1518-17-CM26</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -51622,17 +51622,17 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.818.004-2</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -51661,13 +51661,13 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>1012.19</v>
+        <v>874.46</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>1518-17-CM26</t>
+          <t>2306-892-CM26</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -51687,17 +51687,17 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>61.818.004-2</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
@@ -51707,32 +51707,28 @@
       </c>
       <c r="I803" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K803" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr"/>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>874.46</v>
+        <v>886.86</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2306-892-CM26</t>
+          <t>2989-577-CM26</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -51757,12 +51753,12 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
@@ -51772,12 +51768,12 @@
       </c>
       <c r="I804" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K804" t="inlineStr"/>
@@ -51787,13 +51783,13 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>886.86</v>
+        <v>1591.51</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2989-577-CM26</t>
+          <t>1810-45-CM26</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -51818,12 +51814,12 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
@@ -51833,28 +51829,32 @@
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K805" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>1591.51</v>
+        <v>1012.19</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>1126922-1535-CM26</t>
+          <t>2306-902-CM26</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -51879,12 +51879,12 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
@@ -51894,32 +51894,28 @@
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
         </is>
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K806" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.681.827-0</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr"/>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>3601.36</v>
+        <v>5937.96</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2306-902-CM26</t>
+          <t>1126922-1535-CM26</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -51939,17 +51935,17 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -51959,22 +51955,26 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>VERÓNICA BEATRIZ CÁCERES TORRES</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>9.681.827-0</t>
-        </is>
-      </c>
-      <c r="K807" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>5937.96</v>
+        <v>3601.36</v>
       </c>
     </row>
     <row r="808">
@@ -52362,7 +52362,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>1662-2153-CM26</t>
+          <t>1057532-1698-CM26</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -52387,12 +52387,12 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>61.602.273-3</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
@@ -52421,13 +52421,13 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>992.95</v>
+        <v>846.99</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>1057532-1698-CM26</t>
+          <t>1662-2153-CM26</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -52452,12 +52452,12 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.602.273-3</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
@@ -52486,72 +52486,267 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>846.99</v>
+        <v>992.95</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
+          <t>1301-98-CM26</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M816" s="2" t="n">
+        <v>801.78</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
           <t>696954-89-CM26</t>
         </is>
       </c>
-      <c r="B816" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C816" t="inlineStr">
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D816" t="inlineStr">
+      <c r="D817" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E816" t="inlineStr">
+      <c r="E817" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F816" t="inlineStr">
+      <c r="F817" t="inlineStr">
         <is>
           <t>61.935.400-1</t>
         </is>
       </c>
-      <c r="G816" t="inlineStr">
+      <c r="G817" t="inlineStr">
         <is>
           <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
-      <c r="H816" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
-      <c r="I816" t="inlineStr">
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
-      <c r="J816" t="inlineStr">
+      <c r="J817" t="inlineStr">
         <is>
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr">
+      <c r="K817" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L816" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M816" s="2" t="n">
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M817" s="2" t="n">
         <v>903.37</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2658-1339-CM26</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>69.230.100-5</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M818" s="2" t="n">
+        <v>1786.66</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>1077241-84-CM26</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M819" s="2" t="n">
+        <v>3722.09</v>
       </c>
     </row>
   </sheetData>
